--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_ATICA SEVILLA CB CORIA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_ATICA SEVILLA CB CORIA.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. TEJADA CAMACHO</t>
+          <t>J. CEBOLLA HERRERA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D2" t="n">
-        <v>33.4484</v>
+        <v>31.6285</v>
       </c>
       <c r="E2" t="n">
-        <v>13.525</v>
+        <v>30.9759</v>
       </c>
       <c r="F2" t="n">
-        <v>19.923</v>
+        <v>0.6528000000000003</v>
       </c>
       <c r="G2" t="n">
-        <v>39.2984</v>
+        <v>13.6899</v>
       </c>
       <c r="H2" t="n">
-        <v>25.2776</v>
+        <v>1.3065</v>
       </c>
       <c r="I2" t="n">
-        <v>14.0206</v>
+        <v>12.3832</v>
       </c>
       <c r="J2" t="n">
-        <v>70.8961</v>
+        <v>33.6131</v>
       </c>
       <c r="K2" t="n">
-        <v>41.1826</v>
+        <v>13.8288</v>
       </c>
       <c r="L2" t="n">
-        <v>29.7134</v>
+        <v>19.7842</v>
       </c>
       <c r="M2" t="n">
-        <v>-31.5979</v>
+        <v>-19.9234</v>
       </c>
       <c r="N2" t="n">
-        <v>-15.9051</v>
+        <v>-12.5222</v>
       </c>
       <c r="O2" t="n">
-        <v>-15.6927</v>
+        <v>-7.4011</v>
       </c>
       <c r="P2" t="n">
-        <v>-19.2697</v>
+        <v>6.1145</v>
       </c>
       <c r="Q2" t="n">
-        <v>-73.00320000000001</v>
+        <v>-20.3815</v>
       </c>
       <c r="R2" t="n">
-        <v>53.7334</v>
+        <v>26.4959</v>
       </c>
       <c r="S2" t="n">
-        <v>13.5494</v>
+        <v>-4.984299999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>1.7948</v>
+        <v>-4.285</v>
       </c>
       <c r="U2" t="n">
-        <v>11.7539</v>
+        <v>-0.6992999999999998</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.1296000000000002</v>
+        <v>16.8084</v>
       </c>
       <c r="W2" t="n">
-        <v>13.8368</v>
+        <v>22.0293</v>
       </c>
       <c r="X2" t="n">
-        <v>-13.9664</v>
+        <v>-5.2208</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. CEBOLLA HERRERA</t>
+          <t>A. TEJADA CAMACHO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>25.5475</v>
+        <v>27.9652</v>
       </c>
       <c r="E3" t="n">
-        <v>25.8923</v>
+        <v>11.3329</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.3447999999999997</v>
+        <v>16.6319</v>
       </c>
       <c r="G3" t="n">
-        <v>13.6899</v>
+        <v>39.2984</v>
       </c>
       <c r="H3" t="n">
-        <v>1.3065</v>
+        <v>25.2776</v>
       </c>
       <c r="I3" t="n">
-        <v>12.3832</v>
+        <v>14.0206</v>
       </c>
       <c r="J3" t="n">
-        <v>33.6131</v>
+        <v>70.8961</v>
       </c>
       <c r="K3" t="n">
-        <v>13.8288</v>
+        <v>41.1826</v>
       </c>
       <c r="L3" t="n">
-        <v>19.7842</v>
+        <v>29.7134</v>
       </c>
       <c r="M3" t="n">
-        <v>-19.9234</v>
+        <v>-31.5979</v>
       </c>
       <c r="N3" t="n">
-        <v>-12.5222</v>
+        <v>-15.9051</v>
       </c>
       <c r="O3" t="n">
-        <v>-7.4011</v>
+        <v>-15.6927</v>
       </c>
       <c r="P3" t="n">
-        <v>6.1145</v>
+        <v>-19.2697</v>
       </c>
       <c r="Q3" t="n">
-        <v>-20.3815</v>
+        <v>-73.00320000000001</v>
       </c>
       <c r="R3" t="n">
-        <v>26.4959</v>
+        <v>53.7334</v>
       </c>
       <c r="S3" t="n">
-        <v>-11.0652</v>
+        <v>8.0657</v>
       </c>
       <c r="T3" t="n">
-        <v>-9.3683</v>
+        <v>-0.3972000000000002</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.6966</v>
+        <v>8.4628</v>
       </c>
       <c r="V3" t="n">
-        <v>16.8084</v>
+        <v>-0.1296000000000002</v>
       </c>
       <c r="W3" t="n">
-        <v>22.0293</v>
+        <v>13.8368</v>
       </c>
       <c r="X3" t="n">
-        <v>-5.2208</v>
+        <v>-13.9664</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. LAGHRIDAT</t>
+          <t>M. ORTEGA CARO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D4" t="n">
-        <v>23.2663</v>
+        <v>23.4453</v>
       </c>
       <c r="E4" t="n">
-        <v>11.8289</v>
+        <v>9.406000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>11.4375</v>
+        <v>14.0395</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.02500000000000058</v>
+        <v>18.7125</v>
       </c>
       <c r="H4" t="n">
-        <v>2.4701</v>
+        <v>-3.0712</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.4948</v>
+        <v>21.7834</v>
       </c>
       <c r="J4" t="n">
-        <v>22.6237</v>
+        <v>40.0542</v>
       </c>
       <c r="K4" t="n">
-        <v>17.0958</v>
+        <v>9.573</v>
       </c>
       <c r="L4" t="n">
-        <v>5.5277</v>
+        <v>30.4815</v>
       </c>
       <c r="M4" t="n">
-        <v>-22.6485</v>
+        <v>-21.3416</v>
       </c>
       <c r="N4" t="n">
-        <v>-14.6259</v>
+        <v>-12.6438</v>
       </c>
       <c r="O4" t="n">
-        <v>-8.022499999999999</v>
+        <v>-8.6976</v>
       </c>
       <c r="P4" t="n">
-        <v>4.6324</v>
+        <v>11.8583</v>
       </c>
       <c r="Q4" t="n">
-        <v>-30.943</v>
+        <v>-29.8311</v>
       </c>
       <c r="R4" t="n">
-        <v>35.5751</v>
+        <v>41.6897</v>
       </c>
       <c r="S4" t="n">
-        <v>28.6032</v>
+        <v>-3.9176</v>
       </c>
       <c r="T4" t="n">
-        <v>16.0619</v>
+        <v>-4.5912</v>
       </c>
       <c r="U4" t="n">
-        <v>12.5411</v>
+        <v>0.6737999999999997</v>
       </c>
       <c r="V4" t="n">
-        <v>-9.944099999999999</v>
+        <v>-3.2081</v>
       </c>
       <c r="W4" t="n">
-        <v>4.0861</v>
+        <v>3.774</v>
       </c>
       <c r="X4" t="n">
-        <v>-14.0303</v>
+        <v>-6.9819</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. MORALES ZARCO</t>
+          <t>J. ROBLES ROSADO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>18.8251</v>
+        <v>10.6979</v>
       </c>
       <c r="E5" t="n">
-        <v>13.6184</v>
+        <v>-1.9655</v>
       </c>
       <c r="F5" t="n">
-        <v>5.2063</v>
+        <v>12.6635</v>
       </c>
       <c r="G5" t="n">
-        <v>17.5504</v>
+        <v>-6.9469</v>
       </c>
       <c r="H5" t="n">
-        <v>17.335</v>
+        <v>-0.5355000000000003</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2156000000000001</v>
+        <v>-6.4112</v>
       </c>
       <c r="J5" t="n">
-        <v>37.715</v>
+        <v>7.6632</v>
       </c>
       <c r="K5" t="n">
-        <v>29.7004</v>
+        <v>10.2834</v>
       </c>
       <c r="L5" t="n">
-        <v>8.0145</v>
+        <v>-2.620299999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>-20.1647</v>
+        <v>-14.6099</v>
       </c>
       <c r="N5" t="n">
-        <v>-12.3655</v>
+        <v>-10.8189</v>
       </c>
       <c r="O5" t="n">
-        <v>-7.7991</v>
+        <v>-3.7906</v>
       </c>
       <c r="P5" t="n">
-        <v>-18.3435</v>
+        <v>14.2671</v>
       </c>
       <c r="Q5" t="n">
-        <v>-50.954</v>
+        <v>-21.4932</v>
       </c>
       <c r="R5" t="n">
-        <v>32.6105</v>
+        <v>35.7605</v>
       </c>
       <c r="S5" t="n">
-        <v>28.8253</v>
+        <v>2.8078</v>
       </c>
       <c r="T5" t="n">
-        <v>14.2937</v>
+        <v>-0.09139999999999979</v>
       </c>
       <c r="U5" t="n">
-        <v>14.5315</v>
+        <v>2.8997</v>
       </c>
       <c r="V5" t="n">
-        <v>-9.2074</v>
+        <v>0.5694000000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>12.5639</v>
+        <v>11.9565</v>
       </c>
       <c r="X5" t="n">
-        <v>-21.771</v>
+        <v>-11.3869</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. ROPERO BENIEZ</t>
+          <t>J. CAMPOS CAMPOS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D6" t="n">
-        <v>7.7823</v>
+        <v>10.4524</v>
       </c>
       <c r="E6" t="n">
-        <v>10.8861</v>
+        <v>7.8542</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.1037</v>
+        <v>2.5979</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.0273</v>
+        <v>6.5983</v>
       </c>
       <c r="H6" t="n">
-        <v>2.5656</v>
+        <v>0.9031999999999989</v>
       </c>
       <c r="I6" t="n">
-        <v>-3.5928</v>
+        <v>5.695200000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>11.5214</v>
+        <v>22.095</v>
       </c>
       <c r="K6" t="n">
-        <v>7.527</v>
+        <v>12.7321</v>
       </c>
       <c r="L6" t="n">
-        <v>3.9945</v>
+        <v>9.3629</v>
       </c>
       <c r="M6" t="n">
-        <v>-12.5488</v>
+        <v>-15.4965</v>
       </c>
       <c r="N6" t="n">
-        <v>-4.9616</v>
+        <v>-11.8288</v>
       </c>
       <c r="O6" t="n">
-        <v>-7.5873</v>
+        <v>-3.6678</v>
       </c>
       <c r="P6" t="n">
-        <v>-9.999999999998899e-05</v>
+        <v>11.8585</v>
       </c>
       <c r="Q6" t="n">
-        <v>-8.708500000000001</v>
+        <v>-24.2727</v>
       </c>
       <c r="R6" t="n">
-        <v>8.708499999999999</v>
+        <v>36.131</v>
       </c>
       <c r="S6" t="n">
-        <v>5.0952</v>
+        <v>-4.2924</v>
       </c>
       <c r="T6" t="n">
-        <v>3.0394</v>
+        <v>-4.439699999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>2.0561</v>
+        <v>0.1476</v>
       </c>
       <c r="V6" t="n">
-        <v>3.7142</v>
+        <v>-3.7122</v>
       </c>
       <c r="W6" t="n">
-        <v>5.0337</v>
+        <v>14.4718</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.3195</v>
+        <v>-18.1842</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. ORTEGA CARO</t>
+          <t>J. ROPERO BENIEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>5.6998</v>
+        <v>6.5627</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.198700000000001</v>
+        <v>9.8635</v>
       </c>
       <c r="F7" t="n">
-        <v>7.898299999999999</v>
+        <v>-3.3008</v>
       </c>
       <c r="G7" t="n">
-        <v>18.7125</v>
+        <v>-1.0273</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.0712</v>
+        <v>2.5656</v>
       </c>
       <c r="I7" t="n">
-        <v>21.7834</v>
+        <v>-3.5928</v>
       </c>
       <c r="J7" t="n">
-        <v>40.0542</v>
+        <v>11.5214</v>
       </c>
       <c r="K7" t="n">
-        <v>9.573</v>
+        <v>7.527</v>
       </c>
       <c r="L7" t="n">
-        <v>30.4815</v>
+        <v>3.9945</v>
       </c>
       <c r="M7" t="n">
-        <v>-21.3416</v>
+        <v>-12.5488</v>
       </c>
       <c r="N7" t="n">
-        <v>-12.6438</v>
+        <v>-4.9616</v>
       </c>
       <c r="O7" t="n">
-        <v>-8.6976</v>
+        <v>-7.5873</v>
       </c>
       <c r="P7" t="n">
-        <v>11.8583</v>
+        <v>-9.999999999998899e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>-29.8311</v>
+        <v>-8.708500000000001</v>
       </c>
       <c r="R7" t="n">
-        <v>41.6897</v>
+        <v>8.708499999999999</v>
       </c>
       <c r="S7" t="n">
-        <v>-21.6632</v>
+        <v>3.8758</v>
       </c>
       <c r="T7" t="n">
-        <v>-16.1956</v>
+        <v>2.0169</v>
       </c>
       <c r="U7" t="n">
-        <v>-5.4675</v>
+        <v>1.859</v>
       </c>
       <c r="V7" t="n">
-        <v>-3.2081</v>
+        <v>3.7142</v>
       </c>
       <c r="W7" t="n">
-        <v>3.774</v>
+        <v>5.0337</v>
       </c>
       <c r="X7" t="n">
-        <v>-6.9819</v>
+        <v>-1.3195</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. CAMPOS CAMPOS</t>
+          <t>J. SOSA LLANO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>5.6418</v>
+        <v>4.048100000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>5.772399999999999</v>
+        <v>4.4143</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.130400000000001</v>
+        <v>-0.3660000000000002</v>
       </c>
       <c r="G8" t="n">
-        <v>6.5983</v>
+        <v>2.1494</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9031999999999989</v>
+        <v>-0.8165</v>
       </c>
       <c r="I8" t="n">
-        <v>5.695200000000001</v>
+        <v>2.9657</v>
       </c>
       <c r="J8" t="n">
-        <v>22.095</v>
+        <v>5.077199999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>12.7321</v>
+        <v>-0.2536</v>
       </c>
       <c r="L8" t="n">
-        <v>9.3629</v>
+        <v>5.3309</v>
       </c>
       <c r="M8" t="n">
-        <v>-15.4965</v>
+        <v>-2.928</v>
       </c>
       <c r="N8" t="n">
-        <v>-11.8288</v>
+        <v>-0.5628</v>
       </c>
       <c r="O8" t="n">
-        <v>-3.6678</v>
+        <v>-2.3651</v>
       </c>
       <c r="P8" t="n">
-        <v>11.8585</v>
+        <v>2.2235</v>
       </c>
       <c r="Q8" t="n">
-        <v>-24.2727</v>
+        <v>-1.1117</v>
       </c>
       <c r="R8" t="n">
-        <v>36.131</v>
+        <v>3.335199999999999</v>
       </c>
       <c r="S8" t="n">
-        <v>-9.103</v>
+        <v>0.3031999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>-6.5221</v>
+        <v>0.4486000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>-2.5809</v>
+        <v>-0.1456</v>
       </c>
       <c r="V8" t="n">
-        <v>-3.7122</v>
+        <v>-0.6276999999999999</v>
       </c>
       <c r="W8" t="n">
-        <v>14.4718</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-18.1842</v>
+        <v>-0.6276999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. ROBLES ROSADO</t>
+          <t>J. MORALES ZARCO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D9" t="n">
-        <v>5.527300000000002</v>
+        <v>3.764200000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.2349</v>
+        <v>4.136799999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>9.762199999999998</v>
+        <v>-0.3723000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>-6.9469</v>
+        <v>17.5504</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5355000000000003</v>
+        <v>17.335</v>
       </c>
       <c r="I9" t="n">
-        <v>-6.4112</v>
+        <v>0.2156000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>7.6632</v>
+        <v>37.715</v>
       </c>
       <c r="K9" t="n">
-        <v>10.2834</v>
+        <v>29.7004</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.620299999999999</v>
+        <v>8.0145</v>
       </c>
       <c r="M9" t="n">
-        <v>-14.6099</v>
+        <v>-20.1647</v>
       </c>
       <c r="N9" t="n">
-        <v>-10.8189</v>
+        <v>-12.3655</v>
       </c>
       <c r="O9" t="n">
-        <v>-3.7906</v>
+        <v>-7.7991</v>
       </c>
       <c r="P9" t="n">
-        <v>14.2671</v>
+        <v>-18.3435</v>
       </c>
       <c r="Q9" t="n">
-        <v>-21.4932</v>
+        <v>-50.954</v>
       </c>
       <c r="R9" t="n">
-        <v>35.7605</v>
+        <v>32.6105</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.3624</v>
+        <v>13.7644</v>
       </c>
       <c r="T9" t="n">
-        <v>-2.3611</v>
+        <v>4.8116</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.001500000000000057</v>
+        <v>8.9529</v>
       </c>
       <c r="V9" t="n">
-        <v>0.5694000000000001</v>
+        <v>-9.2074</v>
       </c>
       <c r="W9" t="n">
-        <v>11.9565</v>
+        <v>12.5639</v>
       </c>
       <c r="X9" t="n">
-        <v>-11.3869</v>
+        <v>-21.771</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. SOSA LLANO</t>
+          <t>S. LAGHRIDAT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="D10" t="n">
-        <v>3.9671</v>
+        <v>2.889200000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>4.6532</v>
+        <v>-1.149799999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6861000000000003</v>
+        <v>4.0393</v>
       </c>
       <c r="G10" t="n">
-        <v>2.1494</v>
+        <v>-0.02500000000000058</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.8165</v>
+        <v>2.4701</v>
       </c>
       <c r="I10" t="n">
-        <v>2.9657</v>
+        <v>-2.4948</v>
       </c>
       <c r="J10" t="n">
-        <v>5.077199999999999</v>
+        <v>22.6237</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.2536</v>
+        <v>17.0958</v>
       </c>
       <c r="L10" t="n">
-        <v>5.3309</v>
+        <v>5.5277</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.928</v>
+        <v>-22.6485</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5628</v>
+        <v>-14.6259</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.3651</v>
+        <v>-8.022499999999999</v>
       </c>
       <c r="P10" t="n">
-        <v>2.2235</v>
+        <v>4.6324</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1117</v>
+        <v>-30.943</v>
       </c>
       <c r="R10" t="n">
-        <v>3.335199999999999</v>
+        <v>35.5751</v>
       </c>
       <c r="S10" t="n">
-        <v>0.222</v>
+        <v>8.226799999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6877</v>
+        <v>3.0837</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4657</v>
+        <v>5.1428</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.6276999999999999</v>
+        <v>-9.944099999999999</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>4.0861</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.6276999999999999</v>
+        <v>-14.0303</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C. MONINO MARQUEZ</t>
+          <t>P. QUESADA PONS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,70 +1264,70 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>1.2026</v>
+        <v>2.6816</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8997000000000001</v>
+        <v>5.0577</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3028</v>
+        <v>-2.376</v>
       </c>
       <c r="G11" t="n">
-        <v>1.1862</v>
+        <v>5.968999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>0.925</v>
+        <v>2.2802</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2611</v>
+        <v>3.6889</v>
       </c>
       <c r="J11" t="n">
-        <v>1.0092</v>
+        <v>12.452</v>
       </c>
       <c r="K11" t="n">
-        <v>1.0092</v>
+        <v>7.2675</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>5.1844</v>
       </c>
       <c r="M11" t="n">
-        <v>0.177</v>
+        <v>-6.4826</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.08409999999999999</v>
+        <v>-4.9873</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2611</v>
+        <v>-1.4955</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1853</v>
+        <v>2.2233</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-15.7493</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1853</v>
+        <v>17.9727</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1689</v>
+        <v>-1.2969</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1094</v>
+        <v>0.4877</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0594</v>
+        <v>-1.7848</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-4.214099999999999</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>7.8677</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-12.0818</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.1605</v>
+        <v>1.4795</v>
       </c>
       <c r="E12" t="n">
-        <v>0.7892</v>
+        <v>0.9851</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3713</v>
+        <v>0.4945</v>
       </c>
       <c r="G12" t="n">
         <v>0.3726</v>
@@ -1390,13 +1390,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3979</v>
+        <v>-0.079</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2736</v>
+        <v>-0.07770000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1244</v>
+        <v>-0.0012</v>
       </c>
       <c r="V12" t="n">
         <v>0.63</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P. QUESADA PONS</t>
+          <t>C. MONINO MARQUEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,70 +1420,70 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8850999999999996</v>
+        <v>1.3251</v>
       </c>
       <c r="E13" t="n">
-        <v>5.7952</v>
+        <v>0.9977</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.910000000000001</v>
+        <v>0.3275</v>
       </c>
       <c r="G13" t="n">
-        <v>5.968999999999999</v>
+        <v>1.1862</v>
       </c>
       <c r="H13" t="n">
-        <v>2.2802</v>
+        <v>0.925</v>
       </c>
       <c r="I13" t="n">
-        <v>3.6889</v>
+        <v>0.2611</v>
       </c>
       <c r="J13" t="n">
-        <v>12.452</v>
+        <v>1.0092</v>
       </c>
       <c r="K13" t="n">
-        <v>7.2675</v>
+        <v>1.0092</v>
       </c>
       <c r="L13" t="n">
-        <v>5.1844</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>-6.4826</v>
+        <v>0.177</v>
       </c>
       <c r="N13" t="n">
-        <v>-4.9873</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.4955</v>
+        <v>0.2611</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2233</v>
+        <v>0.1853</v>
       </c>
       <c r="Q13" t="n">
-        <v>-15.7493</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>17.9727</v>
+        <v>0.1853</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.0937</v>
+        <v>-0.0463</v>
       </c>
       <c r="T13" t="n">
-        <v>1.225</v>
+        <v>-0.0115</v>
       </c>
       <c r="U13" t="n">
-        <v>-4.3184</v>
+        <v>-0.0348</v>
       </c>
       <c r="V13" t="n">
-        <v>-4.214099999999999</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>7.8677</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-12.0818</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.7396</v>
+        <v>-1.2805</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.4354</v>
+        <v>-2.1734</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6958999999999996</v>
+        <v>0.8928</v>
       </c>
       <c r="G14" t="n">
         <v>-1.7952</v>
@@ -1546,13 +1546,13 @@
         <v>4.0763</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9255999999999999</v>
+        <v>-0.4666</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3480000000000001</v>
+        <v>-0.08600000000000002</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5775999999999999</v>
+        <v>-0.3805999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>-0.3156</v>
@@ -1579,13 +1579,13 @@
         <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>-4.5687</v>
+        <v>-3.4659</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.9574</v>
+        <v>-2.0761</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.6113</v>
+        <v>-1.3898</v>
       </c>
       <c r="G15" t="n">
         <v>-2.6894</v>
@@ -1624,13 +1624,13 @@
         <v>0.9264999999999999</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.25</v>
+        <v>-0.147</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8754</v>
+        <v>0.005900000000000016</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3746</v>
+        <v>-0.1529</v>
       </c>
       <c r="V15" t="n">
         <v>-0.6294</v>
@@ -1657,13 +1657,13 @@
         <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>-5.1367</v>
+        <v>-5.452199999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>-3.3771</v>
+        <v>-3.8553</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.7596</v>
+        <v>-1.597</v>
       </c>
       <c r="G16" t="n">
         <v>-4.6009</v>
@@ -1702,13 +1702,13 @@
         <v>1.6675</v>
       </c>
       <c r="S16" t="n">
-        <v>1.8419</v>
+        <v>1.5264</v>
       </c>
       <c r="T16" t="n">
-        <v>1.45</v>
+        <v>0.9718</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3919</v>
+        <v>0.5546</v>
       </c>
       <c r="V16" t="n">
         <v>-1.6365</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. LOPEZ MACIAS</t>
+          <t>T. LUCERO BARBEITO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,76 +1732,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="D17" t="n">
-        <v>-6.4996</v>
+        <v>-5.4537</v>
       </c>
       <c r="E17" t="n">
-        <v>-4.5561</v>
+        <v>2.387599999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.9434</v>
+        <v>-7.8411</v>
       </c>
       <c r="G17" t="n">
-        <v>-3.945</v>
+        <v>-6.5573</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.9557</v>
+        <v>-7.6785</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.9892</v>
+        <v>1.120900000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.6999</v>
+        <v>16.3651</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8286</v>
+        <v>8.6799</v>
       </c>
       <c r="L17" t="n">
-        <v>-2.5285</v>
+        <v>7.6851</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.2451</v>
+        <v>-22.9223</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.7844</v>
+        <v>-16.3584</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4608</v>
+        <v>-6.5639</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.1852</v>
+        <v>7.781899999999999</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9264</v>
+        <v>-14.823</v>
       </c>
       <c r="R17" t="n">
-        <v>0.7412</v>
+        <v>22.6049</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.4243</v>
+        <v>-0.007199999999999984</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9849</v>
+        <v>-1.0389</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4395</v>
+        <v>1.032</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.945</v>
+        <v>-6.6713</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.945</v>
+        <v>1.8843</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-8.556099999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. TORRES VELEZ</t>
+          <t>P. LOPEZ MACIAS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,76 +1810,76 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>-15.5472</v>
+        <v>-5.928900000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>-10.9428</v>
+        <v>-4.3056</v>
       </c>
       <c r="F18" t="n">
-        <v>-4.6042</v>
+        <v>-1.6233</v>
       </c>
       <c r="G18" t="n">
-        <v>-9.6343</v>
+        <v>-3.945</v>
       </c>
       <c r="H18" t="n">
-        <v>-5.2527</v>
+        <v>-0.9557</v>
       </c>
       <c r="I18" t="n">
-        <v>-4.381599999999999</v>
+        <v>-2.9892</v>
       </c>
       <c r="J18" t="n">
-        <v>5.3713</v>
+        <v>-1.6999</v>
       </c>
       <c r="K18" t="n">
-        <v>2.9812</v>
+        <v>0.8286</v>
       </c>
       <c r="L18" t="n">
-        <v>2.3903</v>
+        <v>-2.5285</v>
       </c>
       <c r="M18" t="n">
-        <v>-15.0059</v>
+        <v>-2.2451</v>
       </c>
       <c r="N18" t="n">
-        <v>-8.234</v>
+        <v>-1.7844</v>
       </c>
       <c r="O18" t="n">
-        <v>-6.772</v>
+        <v>-0.4608</v>
       </c>
       <c r="P18" t="n">
-        <v>3.335</v>
+        <v>-0.1852</v>
       </c>
       <c r="Q18" t="n">
-        <v>-17.2316</v>
+        <v>-0.9264</v>
       </c>
       <c r="R18" t="n">
-        <v>20.5667</v>
+        <v>0.7412</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5076000000000001</v>
+        <v>-0.8537</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.02459999999999973</v>
+        <v>-0.7342000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5322</v>
+        <v>-0.1194</v>
       </c>
       <c r="V18" t="n">
-        <v>-9.7553</v>
+        <v>-0.945</v>
       </c>
       <c r="W18" t="n">
-        <v>0.9420999999999999</v>
+        <v>-0.945</v>
       </c>
       <c r="X18" t="n">
-        <v>-10.6975</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>T. LUCERO BARBEITO</t>
+          <t>A. RODRIGUEZ LOPEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,76 +1888,76 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D19" t="n">
-        <v>-17.3699</v>
+        <v>-11.2429</v>
       </c>
       <c r="E19" t="n">
-        <v>-5.222099999999999</v>
+        <v>-11.0362</v>
       </c>
       <c r="F19" t="n">
-        <v>-12.1479</v>
+        <v>-0.2067000000000005</v>
       </c>
       <c r="G19" t="n">
-        <v>-6.5573</v>
+        <v>-0.7970999999999995</v>
       </c>
       <c r="H19" t="n">
-        <v>-7.6785</v>
+        <v>1.772</v>
       </c>
       <c r="I19" t="n">
-        <v>1.120900000000001</v>
+        <v>-2.5692</v>
       </c>
       <c r="J19" t="n">
-        <v>16.3651</v>
+        <v>13.3533</v>
       </c>
       <c r="K19" t="n">
-        <v>8.6799</v>
+        <v>10.6184</v>
       </c>
       <c r="L19" t="n">
-        <v>7.6851</v>
+        <v>2.7349</v>
       </c>
       <c r="M19" t="n">
-        <v>-22.9223</v>
+        <v>-14.1504</v>
       </c>
       <c r="N19" t="n">
-        <v>-16.3584</v>
+        <v>-8.8461</v>
       </c>
       <c r="O19" t="n">
-        <v>-6.5639</v>
+        <v>-5.3042</v>
       </c>
       <c r="P19" t="n">
-        <v>7.781899999999999</v>
+        <v>2.9647</v>
       </c>
       <c r="Q19" t="n">
-        <v>-14.823</v>
+        <v>-22.2344</v>
       </c>
       <c r="R19" t="n">
-        <v>22.6049</v>
+        <v>25.199</v>
       </c>
       <c r="S19" t="n">
-        <v>-11.9233</v>
+        <v>-2.1432</v>
       </c>
       <c r="T19" t="n">
-        <v>-8.648400000000001</v>
+        <v>-1.8355</v>
       </c>
       <c r="U19" t="n">
-        <v>-3.2749</v>
+        <v>-0.3073</v>
       </c>
       <c r="V19" t="n">
-        <v>-6.6713</v>
+        <v>-11.2674</v>
       </c>
       <c r="W19" t="n">
-        <v>1.8843</v>
+        <v>-0.3197</v>
       </c>
       <c r="X19" t="n">
-        <v>-8.556099999999999</v>
+        <v>-10.9479</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ LOPEZ</t>
+          <t>J. TORRES VELEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1966,70 +1966,70 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D20" t="n">
-        <v>-18.9895</v>
+        <v>-14.35</v>
       </c>
       <c r="E20" t="n">
-        <v>-16.1428</v>
+        <v>-10.4159</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.8464</v>
+        <v>-3.9341</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.7970999999999995</v>
+        <v>-9.6343</v>
       </c>
       <c r="H20" t="n">
-        <v>1.772</v>
+        <v>-5.2527</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.5692</v>
+        <v>-4.381599999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>13.3533</v>
+        <v>5.3713</v>
       </c>
       <c r="K20" t="n">
-        <v>10.6184</v>
+        <v>2.9812</v>
       </c>
       <c r="L20" t="n">
-        <v>2.7349</v>
+        <v>2.3903</v>
       </c>
       <c r="M20" t="n">
-        <v>-14.1504</v>
+        <v>-15.0059</v>
       </c>
       <c r="N20" t="n">
-        <v>-8.8461</v>
+        <v>-8.234</v>
       </c>
       <c r="O20" t="n">
-        <v>-5.3042</v>
+        <v>-6.772</v>
       </c>
       <c r="P20" t="n">
-        <v>2.9647</v>
+        <v>3.335</v>
       </c>
       <c r="Q20" t="n">
-        <v>-22.2344</v>
+        <v>-17.2316</v>
       </c>
       <c r="R20" t="n">
-        <v>25.199</v>
+        <v>20.5667</v>
       </c>
       <c r="S20" t="n">
-        <v>-9.889799999999999</v>
+        <v>1.7046</v>
       </c>
       <c r="T20" t="n">
-        <v>-6.9424</v>
+        <v>0.5025000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>-2.9472</v>
+        <v>1.2022</v>
       </c>
       <c r="V20" t="n">
-        <v>-11.2674</v>
+        <v>-9.7553</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.3197</v>
+        <v>0.9420999999999999</v>
       </c>
       <c r="X20" t="n">
-        <v>-10.9479</v>
+        <v>-10.6975</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>20</v>
       </c>
       <c r="D21" t="n">
-        <v>-32.7998</v>
+        <v>-31.9476</v>
       </c>
       <c r="E21" t="n">
-        <v>-22.0849</v>
+        <v>-21.8976</v>
       </c>
       <c r="F21" t="n">
-        <v>-10.7152</v>
+        <v>-10.0499</v>
       </c>
       <c r="G21" t="n">
         <v>-25.3721</v>
@@ -2092,13 +2092,13 @@
         <v>11.3025</v>
       </c>
       <c r="S21" t="n">
-        <v>-3.4378</v>
+        <v>-2.5859</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.4263</v>
+        <v>-1.2392</v>
       </c>
       <c r="U21" t="n">
-        <v>-2.0114</v>
+        <v>-1.3468</v>
       </c>
       <c r="V21" t="n">
         <v>-1.951599999999999</v>
@@ -2125,16 +2125,16 @@
         <v>26</v>
       </c>
       <c r="D22" t="n">
-        <v>30.30280000000001</v>
+        <v>47.818</v>
       </c>
       <c r="E22" t="n">
-        <v>19.50820000000001</v>
+        <v>28.53629999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>10.79429999999999</v>
+        <v>19.2827</v>
       </c>
       <c r="G22" t="n">
-        <v>42.1362</v>
+        <v>42.13619999999999</v>
       </c>
       <c r="H22" t="n">
         <v>16.1033</v>
@@ -2161,22 +2161,22 @@
         <v>-98.6127</v>
       </c>
       <c r="P22" t="n">
-        <v>28.71950000000001</v>
+        <v>28.7195</v>
       </c>
       <c r="Q22" t="n">
         <v>-351.1187</v>
       </c>
       <c r="R22" t="n">
-        <v>379.8383</v>
+        <v>379.8383000000001</v>
       </c>
       <c r="S22" t="n">
-        <v>1.939499999999995</v>
+        <v>19.4546</v>
       </c>
       <c r="T22" t="n">
-        <v>-15.5276</v>
+        <v>-6.498799999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>17.4671</v>
+        <v>25.9547</v>
       </c>
       <c r="V22" t="n">
         <v>-42.4933</v>
